--- a/data/raw/legal_corpus/manifest/enterprise/document_manifest.xlsx
+++ b/data/raw/legal_corpus/manifest/enterprise/document_manifest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +736,89 @@
           <t>nhieu_quy_dinh_ve_ho_so_va_thoi_han</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOC_ENTERPRISE_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sua_doi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03 sua doi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ngày 17 tháng 6 năm 2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>03_sua_doi.doc</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>van_ban_khac</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>uu_tien_nghia_vu_quyen_dieu_kien</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
